--- a/single-api/micro-server/micro-api/swagger_modules.xlsx
+++ b/single-api/micro-server/micro-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MicroApi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MicroApi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,11 +470,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -491,35 +491,40 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>服务(Swagger Title)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>平台(Platform)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>模块(Tag)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>接口数</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Case数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>通过率</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>接口覆盖率</t>
         </is>
@@ -531,29 +536,34 @@
           <t>us</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -561,29 +571,34 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>29% (15/52)</t>
         </is>
@@ -591,25 +606,30 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -617,25 +637,30 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -643,29 +668,34 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>4% (2/52)</t>
         </is>
@@ -673,25 +703,30 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>tiktok</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -699,25 +734,30 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -725,29 +765,34 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>25% (13/52)</t>
         </is>
@@ -755,25 +800,30 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>walmart</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -781,25 +831,30 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -807,29 +862,34 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>23% (12/52)</t>
         </is>
@@ -837,25 +897,30 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>instacart</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -863,25 +928,30 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -889,29 +959,34 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>25% (13/52)</t>
         </is>
@@ -919,25 +994,30 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>criteo</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -945,25 +1025,30 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -971,29 +1056,34 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>25% (13/52)</t>
         </is>
@@ -1001,25 +1091,30 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1027,25 +1122,30 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1053,29 +1153,34 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>17% (9/52)</t>
         </is>
@@ -1083,25 +1188,30 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>kroger</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1109,25 +1219,30 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1135,29 +1250,34 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>23% (12/52)</t>
         </is>
@@ -1165,25 +1285,30 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>chewy</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1191,25 +1316,30 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1217,29 +1347,34 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>21% (11/52)</t>
         </is>
@@ -1247,25 +1382,30 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>citrus</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1273,25 +1413,30 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1299,29 +1444,34 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>23% (12/52)</t>
         </is>
@@ -1329,25 +1479,30 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>doordash</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1355,25 +1510,30 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1381,29 +1541,34 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>23% (12/52)</t>
         </is>
@@ -1411,25 +1576,30 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>samsclub</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1437,25 +1607,30 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1463,29 +1638,34 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>13% (7/52)</t>
         </is>
@@ -1493,25 +1673,30 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>bol</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1519,25 +1704,30 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1545,29 +1735,34 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>13% (7/52)</t>
         </is>
@@ -1575,25 +1770,30 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>mercado</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1601,29 +1801,34 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>dsp</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>100% (1/1)</t>
         </is>
@@ -1631,29 +1836,34 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>dsp</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>25% (13/52)</t>
         </is>
@@ -1661,25 +1871,30 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>dsp</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1687,25 +1902,30 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>calendar-center-controller</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1713,29 +1933,34 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>dayparting-controller</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>dayparting-controller</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>23% (12/52)</t>
         </is>
@@ -1743,25 +1968,30 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MicroApi</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>ebay</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>platform-dict-controller</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
         </is>
@@ -1778,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G811"/>
+  <dimension ref="A1:H811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1788,6 +2018,7 @@
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1824,6 +2055,11 @@
       <c r="G1" s="5" t="inlineStr">
         <is>
           <t>场景覆盖</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>

--- a/single-api/micro-server/micro-api/swagger_modules.xlsx
+++ b/single-api/micro-server/micro-api/swagger_modules.xlsx
@@ -92,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -529,6 +532,11 @@
           <t>接口覆盖率</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -568,6 +576,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\amazon\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -603,6 +616,11 @@
           <t>29% (15/52)</t>
         </is>
       </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\amazon\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -634,6 +652,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\amazon\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -665,6 +688,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\tiktok\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -700,6 +728,11 @@
           <t>4% (2/52)</t>
         </is>
       </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\tiktok\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -731,6 +764,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\tiktok\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -762,6 +800,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\walmart\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -797,6 +840,11 @@
           <t>25% (13/52)</t>
         </is>
       </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\walmart\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -828,6 +876,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\walmart\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -859,6 +912,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\instacart\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -894,6 +952,11 @@
           <t>23% (12/52)</t>
         </is>
       </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\instacart\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -925,6 +988,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\instacart\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -956,6 +1024,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\criteo\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -991,6 +1064,11 @@
           <t>25% (13/52)</t>
         </is>
       </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\criteo\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1022,6 +1100,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\criteo\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1053,6 +1136,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\target\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1088,6 +1176,11 @@
           <t>25% (13/52)</t>
         </is>
       </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\target\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1119,6 +1212,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\target\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1150,6 +1248,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\kroger\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1185,6 +1288,11 @@
           <t>17% (9/52)</t>
         </is>
       </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\kroger\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1216,6 +1324,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\kroger\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1247,6 +1360,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\chewy\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1282,6 +1400,11 @@
           <t>23% (12/52)</t>
         </is>
       </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\chewy\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1313,6 +1436,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\chewy\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1344,6 +1472,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\citrus\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1379,6 +1512,11 @@
           <t>21% (11/52)</t>
         </is>
       </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\citrus\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1410,6 +1548,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\citrus\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -1441,6 +1584,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\doordash\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1476,6 +1624,11 @@
           <t>23% (12/52)</t>
         </is>
       </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\doordash\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1507,6 +1660,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\doordash\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1538,6 +1696,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\samsclub\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1573,6 +1736,11 @@
           <t>23% (12/52)</t>
         </is>
       </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\samsclub\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1604,6 +1772,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\samsclub\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1635,6 +1808,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\bol\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1670,6 +1848,11 @@
           <t>13% (7/52)</t>
         </is>
       </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\bol\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1701,6 +1884,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\bol\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1732,6 +1920,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\mercado\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1767,6 +1960,11 @@
           <t>13% (7/52)</t>
         </is>
       </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\mercado\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1798,6 +1996,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\mercado\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1833,6 +2036,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\dsp\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1868,6 +2076,11 @@
           <t>25% (13/52)</t>
         </is>
       </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\dsp\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1899,6 +2112,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\dsp\us\platform-dict-controller</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -1930,6 +2148,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\ebay\us\calendar-center-controller</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -1965,6 +2188,11 @@
           <t>23% (12/52)</t>
         </is>
       </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\ebay\us\dayparting-controller</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -1994,6 +2222,11 @@
       <c r="I46" s="6" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\micro-server\micro-api\ebay\us\platform-dict-controller</t>
         </is>
       </c>
     </row>
